--- a/artfynd/A 42285-2025 artfynd.xlsx
+++ b/artfynd/A 42285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109236143</v>
+        <v>117577492</v>
       </c>
       <c r="B2" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,11 +703,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -721,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>841161.0920156785</v>
+        <v>841183</v>
       </c>
       <c r="R2" t="n">
-        <v>7389093.030514403</v>
+        <v>7389073</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,22 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +776,26 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Träd/buskodling</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsvinbär</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Ribes spicatum</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ribes spicatum</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -790,6 +808,109 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109236143</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tväredet, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>841161</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7389093</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rasmus Gabrielsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rasmus Gabrielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42285-2025 artfynd.xlsx
+++ b/artfynd/A 42285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117577492</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,8 +921,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109236143</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>